--- a/notebooks/XGBoost/predictions_ele.xlsx
+++ b/notebooks/XGBoost/predictions_ele.xlsx
@@ -463,7 +463,7 @@
         <v>70.77</v>
       </c>
       <c r="D2" t="n">
-        <v>69.50811004638672</v>
+        <v>69.50582122802734</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>68.25</v>
       </c>
       <c r="D3" t="n">
-        <v>67.73674774169922</v>
+        <v>67.72753143310547</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         <v>71.51000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>70.33882141113281</v>
+        <v>70.32463836669922</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>72.2</v>
       </c>
       <c r="D5" t="n">
-        <v>70.96688079833984</v>
+        <v>70.92430114746094</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         <v>73.7</v>
       </c>
       <c r="D6" t="n">
-        <v>72.47299957275391</v>
+        <v>72.44402313232422</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>71.98</v>
       </c>
       <c r="D7" t="n">
-        <v>70.71328735351562</v>
+        <v>70.70734405517578</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         <v>71.62</v>
       </c>
       <c r="D8" t="n">
-        <v>70.32733154296875</v>
+        <v>70.33983612060547</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         <v>73.69</v>
       </c>
       <c r="D9" t="n">
-        <v>72.32534027099609</v>
+        <v>72.33244323730469</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         <v>71.7</v>
       </c>
       <c r="D10" t="n">
-        <v>70.67269897460938</v>
+        <v>70.74758148193359</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         <v>72.91</v>
       </c>
       <c r="D11" t="n">
-        <v>71.64386749267578</v>
+        <v>71.62855529785156</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         <v>68.3</v>
       </c>
       <c r="D12" t="n">
-        <v>67.58716583251953</v>
+        <v>67.63673400878906</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         <v>73.55</v>
       </c>
       <c r="D13" t="n">
-        <v>72.13574981689453</v>
+        <v>72.12639617919922</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>69.87449645996094</v>
+        <v>69.91786193847656</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>69.81999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>68.67906188964844</v>
+        <v>68.68129730224609</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>77.14</v>
       </c>
       <c r="D16" t="n">
-        <v>75.22447204589844</v>
+        <v>75.28610229492188</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         <v>73.70999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>72.54795837402344</v>
+        <v>72.56709289550781</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         <v>73.08</v>
       </c>
       <c r="D18" t="n">
-        <v>71.79213714599609</v>
+        <v>71.80031585693359</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>70.43000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>68.73863983154297</v>
+        <v>68.72277069091797</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         <v>76.25</v>
       </c>
       <c r="D20" t="n">
-        <v>74.87026977539062</v>
+        <v>74.86615753173828</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         <v>70.29000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>69.10826873779297</v>
+        <v>69.11007690429688</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         <v>71.98999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>70.66078948974609</v>
+        <v>70.58475494384766</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         <v>71.05</v>
       </c>
       <c r="D23" t="n">
-        <v>69.60935211181641</v>
+        <v>69.55242156982422</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         <v>73.70999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>72.39864349365234</v>
+        <v>72.40657043457031</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         <v>71.31999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>69.99823760986328</v>
+        <v>69.94329833984375</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         <v>69.79000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>68.98644256591797</v>
+        <v>69.00189208984375</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         <v>72.45</v>
       </c>
       <c r="D27" t="n">
-        <v>70.83596801757812</v>
+        <v>70.88545989990234</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         <v>74.88</v>
       </c>
       <c r="D28" t="n">
-        <v>73.30821990966797</v>
+        <v>73.31192016601562</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         <v>72.44</v>
       </c>
       <c r="D29" t="n">
-        <v>71.08389282226562</v>
+        <v>71.12055206298828</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         <v>69.3</v>
       </c>
       <c r="D30" t="n">
-        <v>68.2437744140625</v>
+        <v>68.21578979492188</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         <v>74.48999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>73.43525695800781</v>
+        <v>73.46107482910156</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         <v>70.44</v>
       </c>
       <c r="D32" t="n">
-        <v>69.33402252197266</v>
+        <v>69.26959991455078</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         <v>70.67</v>
       </c>
       <c r="D33" t="n">
-        <v>69.82311248779297</v>
+        <v>69.76589202880859</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>70.87534332275391</v>
+        <v>70.84754943847656</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v>70.43000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>69.43471527099609</v>
+        <v>69.42791748046875</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         <v>72.2</v>
       </c>
       <c r="D36" t="n">
-        <v>70.93784332275391</v>
+        <v>70.91317749023438</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         <v>71.83</v>
       </c>
       <c r="D37" t="n">
-        <v>70.72098541259766</v>
+        <v>70.76008605957031</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         <v>71.12</v>
       </c>
       <c r="D38" t="n">
-        <v>70.15605926513672</v>
+        <v>70.19414520263672</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         <v>71.65000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>70.28861999511719</v>
+        <v>70.35166168212891</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         <v>72.63</v>
       </c>
       <c r="D40" t="n">
-        <v>71.30925750732422</v>
+        <v>71.35294342041016</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         <v>70.94</v>
       </c>
       <c r="D41" t="n">
-        <v>69.84195709228516</v>
+        <v>69.91706848144531</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         <v>70.06</v>
       </c>
       <c r="D42" t="n">
-        <v>69.10550689697266</v>
+        <v>69.10301208496094</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         <v>70</v>
       </c>
       <c r="D43" t="n">
-        <v>68.592529296875</v>
+        <v>68.55364990234375</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         <v>75.36</v>
       </c>
       <c r="D44" t="n">
-        <v>73.72636413574219</v>
+        <v>73.70972442626953</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         <v>69.39</v>
       </c>
       <c r="D45" t="n">
-        <v>68.29789733886719</v>
+        <v>68.32606506347656</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         <v>73.17</v>
       </c>
       <c r="D46" t="n">
-        <v>71.84527587890625</v>
+        <v>71.857421875</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         <v>69.54000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>68.57734680175781</v>
+        <v>68.52753448486328</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         <v>79.87</v>
       </c>
       <c r="D48" t="n">
-        <v>77.44563293457031</v>
+        <v>77.32974243164062</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         <v>79.2</v>
       </c>
       <c r="D49" t="n">
-        <v>77.14621734619141</v>
+        <v>77.13526916503906</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         <v>74.53</v>
       </c>
       <c r="D50" t="n">
-        <v>73.16099548339844</v>
+        <v>73.16263580322266</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         <v>69.75</v>
       </c>
       <c r="D51" t="n">
-        <v>68.44931793212891</v>
+        <v>68.48641967773438</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         <v>70.43000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>69.25196838378906</v>
+        <v>69.22694396972656</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         <v>72.76000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>71.42623138427734</v>
+        <v>71.33269500732422</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         <v>72.04000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>71.03048706054688</v>
+        <v>71.02104949951172</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         <v>73.78</v>
       </c>
       <c r="D55" t="n">
-        <v>72.45082855224609</v>
+        <v>72.46018981933594</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         <v>67.17</v>
       </c>
       <c r="D56" t="n">
-        <v>67.10199737548828</v>
+        <v>67.08310699462891</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         <v>76.16</v>
       </c>
       <c r="D57" t="n">
-        <v>74.51811218261719</v>
+        <v>74.48655700683594</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         <v>75.25</v>
       </c>
       <c r="D58" t="n">
-        <v>73.95146179199219</v>
+        <v>73.95069885253906</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         <v>66.59</v>
       </c>
       <c r="D59" t="n">
-        <v>66.42049407958984</v>
+        <v>66.41677093505859</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         <v>70.68000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>69.66925811767578</v>
+        <v>69.671142578125</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         <v>73.48</v>
       </c>
       <c r="D61" t="n">
-        <v>71.85098266601562</v>
+        <v>71.88488006591797</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         <v>73.19</v>
       </c>
       <c r="D62" t="n">
-        <v>71.40920257568359</v>
+        <v>71.40813446044922</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         <v>72.53</v>
       </c>
       <c r="D63" t="n">
-        <v>71.39365386962891</v>
+        <v>71.37287139892578</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         <v>73.27</v>
       </c>
       <c r="D64" t="n">
-        <v>71.76992034912109</v>
+        <v>71.80502319335938</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         <v>70.22</v>
       </c>
       <c r="D65" t="n">
-        <v>69.36676788330078</v>
+        <v>69.42814636230469</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         <v>71.84</v>
       </c>
       <c r="D66" t="n">
-        <v>70.82325744628906</v>
+        <v>70.82427215576172</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         <v>71.47</v>
       </c>
       <c r="D67" t="n">
-        <v>69.91110229492188</v>
+        <v>69.94975280761719</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         <v>74.86</v>
       </c>
       <c r="D68" t="n">
-        <v>73.77989196777344</v>
+        <v>73.78632354736328</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         <v>72.87</v>
       </c>
       <c r="D69" t="n">
-        <v>71.34531402587891</v>
+        <v>71.56301116943359</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         <v>70.61</v>
       </c>
       <c r="D70" t="n">
-        <v>69.33023071289062</v>
+        <v>69.37889099121094</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         <v>73.05</v>
       </c>
       <c r="D71" t="n">
-        <v>71.70774841308594</v>
+        <v>71.70955657958984</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         <v>72.15000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>71.02065277099609</v>
+        <v>70.96221160888672</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         <v>75.44</v>
       </c>
       <c r="D73" t="n">
-        <v>73.9169921875</v>
+        <v>73.91098785400391</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         <v>72.34</v>
       </c>
       <c r="D74" t="n">
-        <v>71.24604034423828</v>
+        <v>71.23155212402344</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         <v>72.04000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>70.65619659423828</v>
+        <v>70.74993896484375</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         <v>70.33</v>
       </c>
       <c r="D76" t="n">
-        <v>69.25694274902344</v>
+        <v>69.30863952636719</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         <v>76.31999999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>74.80502319335938</v>
+        <v>74.78513336181641</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         <v>72.43000000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>71.27490234375</v>
+        <v>71.26811218261719</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         <v>76.26000000000001</v>
       </c>
       <c r="D79" t="n">
-        <v>74.58694458007812</v>
+        <v>74.57771301269531</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         <v>73.06999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>71.78860473632812</v>
+        <v>71.80317687988281</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         <v>66.56</v>
       </c>
       <c r="D81" t="n">
-        <v>65.42494964599609</v>
+        <v>65.39945220947266</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         <v>75.3</v>
       </c>
       <c r="D82" t="n">
-        <v>73.80522918701172</v>
+        <v>73.81201171875</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         <v>71.98999999999999</v>
       </c>
       <c r="D83" t="n">
-        <v>70.73366546630859</v>
+        <v>70.68827056884766</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         <v>79.38</v>
       </c>
       <c r="D84" t="n">
-        <v>76.73368835449219</v>
+        <v>76.80142211914062</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         <v>76.55</v>
       </c>
       <c r="D85" t="n">
-        <v>75.03580474853516</v>
+        <v>75.06707000732422</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         <v>76.11</v>
       </c>
       <c r="D86" t="n">
-        <v>74.50277709960938</v>
+        <v>74.50986480712891</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/XGBoost/predictions_ele.xlsx
+++ b/notebooks/XGBoost/predictions_ele.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ</t>
+          <t>ОПЖ_прогноз</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>predictions</t>
+          <t>ОПЖ_реальный</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка_абсолютная</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка_относительная_%</t>
         </is>
       </c>
     </row>
@@ -457,13 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="n">
+        <v>69.21921539306641</v>
+      </c>
+      <c r="D2" t="n">
         <v>70.77</v>
       </c>
-      <c r="D2" t="n">
-        <v>69.50582122802734</v>
+      <c r="E2" t="n">
+        <v>1.55078460693359</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.191302256512067</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="n">
+        <v>67.63790893554688</v>
+      </c>
+      <c r="D3" t="n">
         <v>68.25</v>
       </c>
-      <c r="D3" t="n">
-        <v>67.72753143310547</v>
+      <c r="E3" t="n">
+        <v>0.612091064453125</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8968367244734432</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="n">
+        <v>69.9935302734375</v>
+      </c>
+      <c r="D4" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="D4" t="n">
-        <v>70.32463836669922</v>
+      <c r="E4" t="n">
+        <v>1.516469726562505</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.120640087487771</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="n">
+        <v>70.88333129882812</v>
+      </c>
+      <c r="D5" t="n">
         <v>72.2</v>
       </c>
-      <c r="D5" t="n">
-        <v>70.92430114746094</v>
+      <c r="E5" t="n">
+        <v>1.316668701171878</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.823640860348861</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="n">
+        <v>71.88725280761719</v>
+      </c>
+      <c r="D6" t="n">
         <v>73.7</v>
       </c>
-      <c r="D6" t="n">
-        <v>72.44402313232422</v>
+      <c r="E6" t="n">
+        <v>1.812747192382815</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.459629840410876</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="n">
+        <v>70.26525115966797</v>
+      </c>
+      <c r="D7" t="n">
         <v>71.98</v>
       </c>
-      <c r="D7" t="n">
-        <v>70.70734405517578</v>
+      <c r="E7" t="n">
+        <v>1.714748840332035</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.382257349724972</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="n">
+        <v>69.84947204589844</v>
+      </c>
+      <c r="D8" t="n">
         <v>71.62</v>
       </c>
-      <c r="D8" t="n">
-        <v>70.33983612060547</v>
+      <c r="E8" t="n">
+        <v>1.770527954101567</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.472113870569069</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="n">
+        <v>72.11544036865234</v>
+      </c>
+      <c r="D9" t="n">
         <v>73.69</v>
       </c>
-      <c r="D9" t="n">
-        <v>72.33244323730469</v>
+      <c r="E9" t="n">
+        <v>1.574559631347654</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.13673447054913</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="n">
+        <v>70.76146697998047</v>
+      </c>
+      <c r="D10" t="n">
         <v>71.7</v>
       </c>
-      <c r="D10" t="n">
-        <v>70.74758148193359</v>
+      <c r="E10" t="n">
+        <v>0.9385330200195341</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.308972133918457</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="n">
+        <v>71.39675140380859</v>
+      </c>
+      <c r="D11" t="n">
         <v>72.91</v>
       </c>
-      <c r="D11" t="n">
-        <v>71.62855529785156</v>
+      <c r="E11" t="n">
+        <v>1.513248596191403</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.075502120684958</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +687,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="n">
+        <v>67.25455474853516</v>
+      </c>
+      <c r="D12" t="n">
         <v>68.3</v>
       </c>
-      <c r="D12" t="n">
-        <v>67.63673400878906</v>
+      <c r="E12" t="n">
+        <v>1.045445251464841</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.530666546800646</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +709,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="n">
+        <v>71.69918823242188</v>
+      </c>
+      <c r="D13" t="n">
         <v>73.55</v>
       </c>
-      <c r="D13" t="n">
-        <v>72.12639617919922</v>
+      <c r="E13" t="n">
+        <v>1.850811767578122</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.516399412070867</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +731,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="n">
+        <v>69.74142456054688</v>
+      </c>
+      <c r="D14" t="n">
         <v>71.18000000000001</v>
       </c>
-      <c r="D14" t="n">
-        <v>69.91786193847656</v>
+      <c r="E14" t="n">
+        <v>1.438575439453132</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.021038830364051</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +753,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="n">
+        <v>68.56122589111328</v>
+      </c>
+      <c r="D15" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="D15" t="n">
-        <v>68.68129730224609</v>
+      <c r="E15" t="n">
+        <v>1.258774108886712</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.802884716251378</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +775,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="n">
+        <v>74.63931274414062</v>
+      </c>
+      <c r="D16" t="n">
         <v>77.14</v>
       </c>
-      <c r="D16" t="n">
-        <v>75.28610229492188</v>
+      <c r="E16" t="n">
+        <v>2.500687255859376</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.24175169284337</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="n">
+        <v>72.05408477783203</v>
+      </c>
+      <c r="D17" t="n">
         <v>73.70999999999999</v>
       </c>
-      <c r="D17" t="n">
-        <v>72.56709289550781</v>
+      <c r="E17" t="n">
+        <v>1.655915222167962</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.246527231268434</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +819,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C18" t="n">
+        <v>71.61508178710938</v>
+      </c>
+      <c r="D18" t="n">
         <v>73.08</v>
       </c>
-      <c r="D18" t="n">
-        <v>71.80031585693359</v>
+      <c r="E18" t="n">
+        <v>1.464918212890623</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.004540521196803</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +841,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C19" t="n">
+        <v>68.05660247802734</v>
+      </c>
+      <c r="D19" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="D19" t="n">
-        <v>68.72277069091797</v>
+      <c r="E19" t="n">
+        <v>2.373397521972663</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.369867275270003</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +863,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C20" t="n">
+        <v>74.3035888671875</v>
+      </c>
+      <c r="D20" t="n">
         <v>76.25</v>
       </c>
-      <c r="D20" t="n">
-        <v>74.86615753173828</v>
+      <c r="E20" t="n">
+        <v>1.9464111328125</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.552670338114754</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +885,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C21" t="n">
+        <v>68.88254547119141</v>
+      </c>
+      <c r="D21" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="D21" t="n">
-        <v>69.11007690429688</v>
+      <c r="E21" t="n">
+        <v>1.4074545288086</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.002353860874377</v>
       </c>
     </row>
     <row r="22">
@@ -777,13 +907,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C22" t="n">
+        <v>70.41399383544922</v>
+      </c>
+      <c r="D22" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="D22" t="n">
-        <v>70.58475494384766</v>
+      <c r="E22" t="n">
+        <v>1.576006164550776</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.189201506529763</v>
       </c>
     </row>
     <row r="23">
@@ -793,13 +929,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C23" t="n">
+        <v>69.17040252685547</v>
+      </c>
+      <c r="D23" t="n">
         <v>71.05</v>
       </c>
-      <c r="D23" t="n">
-        <v>69.55242156982422</v>
+      <c r="E23" t="n">
+        <v>1.879597473144528</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.64545738655106</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +951,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C24" t="n">
+        <v>71.82840728759766</v>
+      </c>
+      <c r="D24" t="n">
         <v>73.70999999999999</v>
       </c>
-      <c r="D24" t="n">
-        <v>72.40657043457031</v>
+      <c r="E24" t="n">
+        <v>1.881592712402337</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.552696665855837</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +973,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C25" t="n">
+        <v>69.65876007080078</v>
+      </c>
+      <c r="D25" t="n">
         <v>71.31999999999999</v>
       </c>
-      <c r="D25" t="n">
-        <v>69.94329833984375</v>
+      <c r="E25" t="n">
+        <v>1.661239929199212</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.32927640100843</v>
       </c>
     </row>
     <row r="26">
@@ -841,13 +995,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C26" t="n">
+        <v>69.17428588867188</v>
+      </c>
+      <c r="D26" t="n">
         <v>69.79000000000001</v>
       </c>
-      <c r="D26" t="n">
-        <v>69.00189208984375</v>
+      <c r="E26" t="n">
+        <v>0.6157141113281313</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8822383025191736</v>
       </c>
     </row>
     <row r="27">
@@ -857,13 +1017,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C27" t="n">
+        <v>70.63580322265625</v>
+      </c>
+      <c r="D27" t="n">
         <v>72.45</v>
       </c>
-      <c r="D27" t="n">
-        <v>70.88545989990234</v>
+      <c r="E27" t="n">
+        <v>1.814196777343753</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.504067325526229</v>
       </c>
     </row>
     <row r="28">
@@ -873,13 +1039,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C28" t="n">
+        <v>72.30496215820312</v>
+      </c>
+      <c r="D28" t="n">
         <v>74.88</v>
       </c>
-      <c r="D28" t="n">
-        <v>73.31192016601562</v>
+      <c r="E28" t="n">
+        <v>2.57503784179687</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.438886006673171</v>
       </c>
     </row>
     <row r="29">
@@ -889,13 +1061,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C29" t="n">
+        <v>71.00884246826172</v>
+      </c>
+      <c r="D29" t="n">
         <v>72.44</v>
       </c>
-      <c r="D29" t="n">
-        <v>71.12055206298828</v>
+      <c r="E29" t="n">
+        <v>1.431157531738279</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.975645405491826</v>
       </c>
     </row>
     <row r="30">
@@ -905,13 +1083,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C30" t="n">
+        <v>67.84829711914062</v>
+      </c>
+      <c r="D30" t="n">
         <v>69.3</v>
       </c>
-      <c r="D30" t="n">
-        <v>68.21578979492188</v>
+      <c r="E30" t="n">
+        <v>1.451702880859372</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.094809351889426</v>
       </c>
     </row>
     <row r="31">
@@ -921,13 +1105,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C31" t="n">
+        <v>72.96413421630859</v>
+      </c>
+      <c r="D31" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="D31" t="n">
-        <v>73.46107482910156</v>
+      <c r="E31" t="n">
+        <v>1.525865783691401</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.048416946826958</v>
       </c>
     </row>
     <row r="32">
@@ -937,13 +1127,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C32" t="n">
+        <v>69.34970855712891</v>
+      </c>
+      <c r="D32" t="n">
         <v>70.44</v>
       </c>
-      <c r="D32" t="n">
-        <v>69.26959991455078</v>
+      <c r="E32" t="n">
+        <v>1.090291442871091</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.547829987040164</v>
       </c>
     </row>
     <row r="33">
@@ -953,13 +1149,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C33" t="n">
+        <v>69.93154907226562</v>
+      </c>
+      <c r="D33" t="n">
         <v>70.67</v>
       </c>
-      <c r="D33" t="n">
-        <v>69.76589202880859</v>
+      <c r="E33" t="n">
+        <v>0.7384509277343767</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.044928438848701</v>
       </c>
     </row>
     <row r="34">
@@ -969,13 +1171,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C34" t="n">
+        <v>70.73141479492188</v>
+      </c>
+      <c r="D34" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D34" t="n">
-        <v>70.84754943847656</v>
+      <c r="E34" t="n">
+        <v>1.368585205078119</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.898176428679777</v>
       </c>
     </row>
     <row r="35">
@@ -985,13 +1193,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C35" t="n">
+        <v>69.58677673339844</v>
+      </c>
+      <c r="D35" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="D35" t="n">
-        <v>69.42791748046875</v>
+      <c r="E35" t="n">
+        <v>0.8432232666015693</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.197250130060442</v>
       </c>
     </row>
     <row r="36">
@@ -1001,13 +1215,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C36" t="n">
+        <v>70.78486633300781</v>
+      </c>
+      <c r="D36" t="n">
         <v>72.2</v>
       </c>
-      <c r="D36" t="n">
-        <v>70.91317749023438</v>
+      <c r="E36" t="n">
+        <v>1.41513366699219</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.960018929352064</v>
       </c>
     </row>
     <row r="37">
@@ -1017,13 +1237,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C37" t="n">
+        <v>70.68997192382812</v>
+      </c>
+      <c r="D37" t="n">
         <v>71.83</v>
       </c>
-      <c r="D37" t="n">
-        <v>70.76008605957031</v>
+      <c r="E37" t="n">
+        <v>1.140028076171873</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.587119693960564</v>
       </c>
     </row>
     <row r="38">
@@ -1033,13 +1259,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C38" t="n">
+        <v>70.36371612548828</v>
+      </c>
+      <c r="D38" t="n">
         <v>71.12</v>
       </c>
-      <c r="D38" t="n">
-        <v>70.19414520263672</v>
+      <c r="E38" t="n">
+        <v>0.7562838745117233</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.063391274622783</v>
       </c>
     </row>
     <row r="39">
@@ -1049,13 +1281,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C39" t="n">
+        <v>69.88132476806641</v>
+      </c>
+      <c r="D39" t="n">
         <v>71.65000000000001</v>
       </c>
-      <c r="D39" t="n">
-        <v>70.35166168212891</v>
+      <c r="E39" t="n">
+        <v>1.768675231933599</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.468492996418143</v>
       </c>
     </row>
     <row r="40">
@@ -1065,13 +1303,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C40" t="n">
+        <v>70.94296264648438</v>
+      </c>
+      <c r="D40" t="n">
         <v>72.63</v>
       </c>
-      <c r="D40" t="n">
-        <v>71.35294342041016</v>
+      <c r="E40" t="n">
+        <v>1.68703735351562</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.322783083458103</v>
       </c>
     </row>
     <row r="41">
@@ -1081,13 +1325,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C41" t="n">
+        <v>70.01546478271484</v>
+      </c>
+      <c r="D41" t="n">
         <v>70.94</v>
       </c>
-      <c r="D41" t="n">
-        <v>69.91706848144531</v>
+      <c r="E41" t="n">
+        <v>0.924535217285154</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.303263627410705</v>
       </c>
     </row>
     <row r="42">
@@ -1097,13 +1347,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C42" t="n">
+        <v>68.87521362304688</v>
+      </c>
+      <c r="D42" t="n">
         <v>70.06</v>
       </c>
-      <c r="D42" t="n">
-        <v>69.10301208496094</v>
+      <c r="E42" t="n">
+        <v>1.184786376953127</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.691102450689591</v>
       </c>
     </row>
     <row r="43">
@@ -1113,13 +1369,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C43" t="n">
+        <v>68.35826873779297</v>
+      </c>
+      <c r="D43" t="n">
         <v>70</v>
       </c>
-      <c r="D43" t="n">
-        <v>68.55364990234375</v>
+      <c r="E43" t="n">
+        <v>1.641731262207031</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.345330374581473</v>
       </c>
     </row>
     <row r="44">
@@ -1129,13 +1391,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C44" t="n">
+        <v>72.64363098144531</v>
+      </c>
+      <c r="D44" t="n">
         <v>75.36</v>
       </c>
-      <c r="D44" t="n">
-        <v>73.70972442626953</v>
+      <c r="E44" t="n">
+        <v>2.716369018554687</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.604523644578937</v>
       </c>
     </row>
     <row r="45">
@@ -1145,13 +1413,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C45" t="n">
+        <v>67.87821960449219</v>
+      </c>
+      <c r="D45" t="n">
         <v>69.39</v>
       </c>
-      <c r="D45" t="n">
-        <v>68.32606506347656</v>
+      <c r="E45" t="n">
+        <v>1.511780395507813</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.178671848260287</v>
       </c>
     </row>
     <row r="46">
@@ -1161,13 +1435,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C46" t="n">
+        <v>71.84815979003906</v>
+      </c>
+      <c r="D46" t="n">
         <v>73.17</v>
       </c>
-      <c r="D46" t="n">
-        <v>71.857421875</v>
+      <c r="E46" t="n">
+        <v>1.321840209960939</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.806533018943473</v>
       </c>
     </row>
     <row r="47">
@@ -1177,13 +1457,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C47" t="n">
+        <v>68.60189819335938</v>
+      </c>
+      <c r="D47" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="D47" t="n">
-        <v>68.52753448486328</v>
+      <c r="E47" t="n">
+        <v>0.9381018066406313</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.349010363302604</v>
       </c>
     </row>
     <row r="48">
@@ -1193,13 +1479,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C48" t="n">
+        <v>77.24663543701172</v>
+      </c>
+      <c r="D48" t="n">
         <v>79.87</v>
       </c>
-      <c r="D48" t="n">
-        <v>77.32974243164062</v>
+      <c r="E48" t="n">
+        <v>2.623364562988286</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.284543086250514</v>
       </c>
     </row>
     <row r="49">
@@ -1209,13 +1501,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C49" t="n">
+        <v>76.98065948486328</v>
+      </c>
+      <c r="D49" t="n">
         <v>79.2</v>
       </c>
-      <c r="D49" t="n">
-        <v>77.13526916503906</v>
+      <c r="E49" t="n">
+        <v>2.219340515136722</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.802197620122123</v>
       </c>
     </row>
     <row r="50">
@@ -1225,13 +1523,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C50" t="n">
+        <v>72.47671508789062</v>
+      </c>
+      <c r="D50" t="n">
         <v>74.53</v>
       </c>
-      <c r="D50" t="n">
-        <v>73.16263580322266</v>
+      <c r="E50" t="n">
+        <v>2.053284912109376</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.754977743337416</v>
       </c>
     </row>
     <row r="51">
@@ -1241,13 +1545,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C51" t="n">
+        <v>68.26071929931641</v>
+      </c>
+      <c r="D51" t="n">
         <v>69.75</v>
       </c>
-      <c r="D51" t="n">
-        <v>68.48641967773438</v>
+      <c r="E51" t="n">
+        <v>1.489280700683594</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.135169463345654</v>
       </c>
     </row>
     <row r="52">
@@ -1257,13 +1567,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C52" t="n">
+        <v>69.20797729492188</v>
+      </c>
+      <c r="D52" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="D52" t="n">
-        <v>69.22694396972656</v>
+      <c r="E52" t="n">
+        <v>1.222022705078132</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.735088321848831</v>
       </c>
     </row>
     <row r="53">
@@ -1273,13 +1589,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C53" t="n">
+        <v>70.99195861816406</v>
+      </c>
+      <c r="D53" t="n">
         <v>72.76000000000001</v>
       </c>
-      <c r="D53" t="n">
-        <v>71.33269500732422</v>
+      <c r="E53" t="n">
+        <v>1.768041381835943</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.429963416487002</v>
       </c>
     </row>
     <row r="54">
@@ -1289,13 +1611,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C54" t="n">
+        <v>70.99642181396484</v>
+      </c>
+      <c r="D54" t="n">
         <v>72.04000000000001</v>
       </c>
-      <c r="D54" t="n">
-        <v>71.02104949951172</v>
+      <c r="E54" t="n">
+        <v>1.043578186035163</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.448609364290897</v>
       </c>
     </row>
     <row r="55">
@@ -1305,13 +1633,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C55" t="n">
+        <v>72.06686401367188</v>
+      </c>
+      <c r="D55" t="n">
         <v>73.78</v>
       </c>
-      <c r="D55" t="n">
-        <v>72.46018981933594</v>
+      <c r="E55" t="n">
+        <v>1.713135986328126</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.321951729910716</v>
       </c>
     </row>
     <row r="56">
@@ -1321,13 +1655,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C56" t="n">
+        <v>67.28253936767578</v>
+      </c>
+      <c r="D56" t="n">
         <v>67.17</v>
       </c>
-      <c r="D56" t="n">
-        <v>67.08310699462891</v>
+      <c r="E56" t="n">
+        <v>-0.1125393676757795</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.167544093606937</v>
       </c>
     </row>
     <row r="57">
@@ -1337,13 +1677,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C57" t="n">
+        <v>73.86916351318359</v>
+      </c>
+      <c r="D57" t="n">
         <v>76.16</v>
       </c>
-      <c r="D57" t="n">
-        <v>74.48655700683594</v>
+      <c r="E57" t="n">
+        <v>2.290836486816403</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.007926059370277</v>
       </c>
     </row>
     <row r="58">
@@ -1353,13 +1699,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C58" t="n">
+        <v>73.971435546875</v>
+      </c>
+      <c r="D58" t="n">
         <v>75.25</v>
       </c>
-      <c r="D58" t="n">
-        <v>73.95069885253906</v>
+      <c r="E58" t="n">
+        <v>1.278564453125</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.699088974252492</v>
       </c>
     </row>
     <row r="59">
@@ -1369,13 +1721,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C59" t="n">
+        <v>66.74309539794922</v>
+      </c>
+      <c r="D59" t="n">
         <v>66.59</v>
       </c>
-      <c r="D59" t="n">
-        <v>66.41677093505859</v>
+      <c r="E59" t="n">
+        <v>-0.1530953979492153</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.2299074905379416</v>
       </c>
     </row>
     <row r="60">
@@ -1385,13 +1743,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C60" t="n">
+        <v>69.70540618896484</v>
+      </c>
+      <c r="D60" t="n">
         <v>70.68000000000001</v>
       </c>
-      <c r="D60" t="n">
-        <v>69.671142578125</v>
+      <c r="E60" t="n">
+        <v>0.9745938110351631</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.378882019008437</v>
       </c>
     </row>
     <row r="61">
@@ -1401,13 +1765,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C61" t="n">
+        <v>71.04617309570312</v>
+      </c>
+      <c r="D61" t="n">
         <v>73.48</v>
       </c>
-      <c r="D61" t="n">
-        <v>71.88488006591797</v>
+      <c r="E61" t="n">
+        <v>2.433826904296879</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.312230408678387</v>
       </c>
     </row>
     <row r="62">
@@ -1417,13 +1787,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C62" t="n">
+        <v>70.84047698974609</v>
+      </c>
+      <c r="D62" t="n">
         <v>73.19</v>
       </c>
-      <c r="D62" t="n">
-        <v>71.40813446044922</v>
+      <c r="E62" t="n">
+        <v>2.349523010253904</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.210169436062173</v>
       </c>
     </row>
     <row r="63">
@@ -1433,13 +1809,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C63" t="n">
+        <v>71.07506561279297</v>
+      </c>
+      <c r="D63" t="n">
         <v>72.53</v>
       </c>
-      <c r="D63" t="n">
-        <v>71.37287139892578</v>
+      <c r="E63" t="n">
+        <v>1.454934387207032</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.005975992288753</v>
       </c>
     </row>
     <row r="64">
@@ -1449,13 +1831,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C64" t="n">
+        <v>71.60547637939453</v>
+      </c>
+      <c r="D64" t="n">
         <v>73.27</v>
       </c>
-      <c r="D64" t="n">
-        <v>71.80502319335938</v>
+      <c r="E64" t="n">
+        <v>1.664523620605465</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.27176691770911</v>
       </c>
     </row>
     <row r="65">
@@ -1465,13 +1853,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C65" t="n">
+        <v>69.60078430175781</v>
+      </c>
+      <c r="D65" t="n">
         <v>70.22</v>
       </c>
-      <c r="D65" t="n">
-        <v>69.42814636230469</v>
+      <c r="E65" t="n">
+        <v>0.6192156982421864</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.8818224127630111</v>
       </c>
     </row>
     <row r="66">
@@ -1481,13 +1875,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C66" t="n">
+        <v>70.63391876220703</v>
+      </c>
+      <c r="D66" t="n">
         <v>71.84</v>
       </c>
-      <c r="D66" t="n">
-        <v>70.82427215576172</v>
+      <c r="E66" t="n">
+        <v>1.206081237792972</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.678843593809816</v>
       </c>
     </row>
     <row r="67">
@@ -1497,13 +1897,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C67" t="n">
+        <v>69.537841796875</v>
+      </c>
+      <c r="D67" t="n">
         <v>71.47</v>
       </c>
-      <c r="D67" t="n">
-        <v>69.94975280761719</v>
+      <c r="E67" t="n">
+        <v>1.932158203124999</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.703453481355812</v>
       </c>
     </row>
     <row r="68">
@@ -1513,13 +1919,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C68" t="n">
+        <v>73.59883880615234</v>
+      </c>
+      <c r="D68" t="n">
         <v>74.86</v>
       </c>
-      <c r="D68" t="n">
-        <v>73.78632354736328</v>
+      <c r="E68" t="n">
+        <v>1.261161193847656</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.684693018765236</v>
       </c>
     </row>
     <row r="69">
@@ -1529,13 +1941,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C69" t="n">
+        <v>70.75257873535156</v>
+      </c>
+      <c r="D69" t="n">
         <v>72.87</v>
       </c>
-      <c r="D69" t="n">
-        <v>71.56301116943359</v>
+      <c r="E69" t="n">
+        <v>2.117421264648442</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.905751701178046</v>
       </c>
     </row>
     <row r="70">
@@ -1545,13 +1963,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C70" t="n">
+        <v>69.19623565673828</v>
+      </c>
+      <c r="D70" t="n">
         <v>70.61</v>
       </c>
-      <c r="D70" t="n">
-        <v>69.37889099121094</v>
+      <c r="E70" t="n">
+        <v>1.413764343261718</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.002215469850896</v>
       </c>
     </row>
     <row r="71">
@@ -1561,13 +1985,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C71" t="n">
+        <v>71.39559173583984</v>
+      </c>
+      <c r="D71" t="n">
         <v>73.05</v>
       </c>
-      <c r="D71" t="n">
-        <v>71.70955657958984</v>
+      <c r="E71" t="n">
+        <v>1.654408264160153</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.264761484134365</v>
       </c>
     </row>
     <row r="72">
@@ -1577,13 +2007,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C72" t="n">
+        <v>70.75215911865234</v>
+      </c>
+      <c r="D72" t="n">
         <v>72.15000000000001</v>
       </c>
-      <c r="D72" t="n">
-        <v>70.96221160888672</v>
+      <c r="E72" t="n">
+        <v>1.397840881347662</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.937409398957258</v>
       </c>
     </row>
     <row r="73">
@@ -1593,13 +2029,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C73" t="n">
+        <v>73.79697418212891</v>
+      </c>
+      <c r="D73" t="n">
         <v>75.44</v>
       </c>
-      <c r="D73" t="n">
-        <v>73.91098785400391</v>
+      <c r="E73" t="n">
+        <v>1.643025817871091</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.177923936732624</v>
       </c>
     </row>
     <row r="74">
@@ -1609,13 +2051,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C74" t="n">
+        <v>71.14756774902344</v>
+      </c>
+      <c r="D74" t="n">
         <v>72.34</v>
       </c>
-      <c r="D74" t="n">
-        <v>71.23155212402344</v>
+      <c r="E74" t="n">
+        <v>1.192432250976566</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.64837192559658</v>
       </c>
     </row>
     <row r="75">
@@ -1625,13 +2073,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C75" t="n">
+        <v>70.57736206054688</v>
+      </c>
+      <c r="D75" t="n">
         <v>72.04000000000001</v>
       </c>
-      <c r="D75" t="n">
-        <v>70.74993896484375</v>
+      <c r="E75" t="n">
+        <v>1.462637939453131</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.030313630556817</v>
       </c>
     </row>
     <row r="76">
@@ -1641,13 +2095,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C76" t="n">
+        <v>69.28621673583984</v>
+      </c>
+      <c r="D76" t="n">
         <v>70.33</v>
       </c>
-      <c r="D76" t="n">
-        <v>69.30863952636719</v>
+      <c r="E76" t="n">
+        <v>1.043783264160155</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.484122371904101</v>
       </c>
     </row>
     <row r="77">
@@ -1657,13 +2117,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C77" t="n">
+        <v>74.25751495361328</v>
+      </c>
+      <c r="D77" t="n">
         <v>76.31999999999999</v>
       </c>
-      <c r="D77" t="n">
-        <v>74.78513336181641</v>
+      <c r="E77" t="n">
+        <v>2.062485046386712</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.702417513609424</v>
       </c>
     </row>
     <row r="78">
@@ -1673,13 +2139,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C78" t="n">
+        <v>71.14673614501953</v>
+      </c>
+      <c r="D78" t="n">
         <v>72.43000000000001</v>
       </c>
-      <c r="D78" t="n">
-        <v>71.26811218261719</v>
+      <c r="E78" t="n">
+        <v>1.283263854980476</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.771729745934662</v>
       </c>
     </row>
     <row r="79">
@@ -1689,13 +2161,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C79" t="n">
+        <v>73.72452545166016</v>
+      </c>
+      <c r="D79" t="n">
         <v>76.26000000000001</v>
       </c>
-      <c r="D79" t="n">
-        <v>74.57771301269531</v>
+      <c r="E79" t="n">
+        <v>2.535474548339849</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3.324776486152437</v>
       </c>
     </row>
     <row r="80">
@@ -1705,13 +2183,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C80" t="n">
+        <v>71.62841796875</v>
+      </c>
+      <c r="D80" t="n">
         <v>73.06999999999999</v>
       </c>
-      <c r="D80" t="n">
-        <v>71.80317687988281</v>
+      <c r="E80" t="n">
+        <v>1.441582031249993</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.972878104899402</v>
       </c>
     </row>
     <row r="81">
@@ -1721,13 +2205,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C81" t="n">
+        <v>65.32554626464844</v>
+      </c>
+      <c r="D81" t="n">
         <v>66.56</v>
       </c>
-      <c r="D81" t="n">
-        <v>65.39945220947266</v>
+      <c r="E81" t="n">
+        <v>1.234453735351565</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.854648039891173</v>
       </c>
     </row>
     <row r="82">
@@ -1737,13 +2227,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C82" t="n">
+        <v>73.85070037841797</v>
+      </c>
+      <c r="D82" t="n">
         <v>75.3</v>
       </c>
-      <c r="D82" t="n">
-        <v>73.81201171875</v>
+      <c r="E82" t="n">
+        <v>1.449299621582028</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.924700692672017</v>
       </c>
     </row>
     <row r="83">
@@ -1753,13 +2249,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C83" t="n">
+        <v>70.58260345458984</v>
+      </c>
+      <c r="D83" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="D83" t="n">
-        <v>70.68827056884766</v>
+      <c r="E83" t="n">
+        <v>1.407396545410151</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.95498895042388</v>
       </c>
     </row>
     <row r="84">
@@ -1769,13 +2271,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C84" t="n">
+        <v>76.65907287597656</v>
+      </c>
+      <c r="D84" t="n">
         <v>79.38</v>
       </c>
-      <c r="D84" t="n">
-        <v>76.80142211914062</v>
+      <c r="E84" t="n">
+        <v>2.720927124023433</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3.427723764201856</v>
       </c>
     </row>
     <row r="85">
@@ -1785,13 +2293,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C85" t="n">
+        <v>74.58950805664062</v>
+      </c>
+      <c r="D85" t="n">
         <v>76.55</v>
       </c>
-      <c r="D85" t="n">
-        <v>75.06707000732422</v>
+      <c r="E85" t="n">
+        <v>1.960491943359372</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.561060670619689</v>
       </c>
     </row>
     <row r="86">
@@ -1801,13 +2315,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C86" t="n">
+        <v>73.95211029052734</v>
+      </c>
+      <c r="D86" t="n">
         <v>76.11</v>
       </c>
-      <c r="D86" t="n">
-        <v>74.50986480712891</v>
+      <c r="E86" t="n">
+        <v>2.157889709472656</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2.835224950036336</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/XGBoost/predictions_ele.xlsx
+++ b/notebooks/XGBoost/predictions_ele.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_реальный</t>
+          <t>ОПЖ</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
